--- a/docs/Contratacion/Plantilla masivos.xlsx
+++ b/docs/Contratacion/Plantilla masivos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manuel.espinosa\Desktop\GH DOCS CONTRATACION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SJSEGURIDAD\docs\Contratacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F094314A-B0E1-40D6-B86C-CBCF8E155BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098A47D6-9E16-40A3-9FAC-258EC933FB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="718" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="EMPLEADOS" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMPLEADOS!$A$2:$BJ$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMPLEADOS!$A$2:$BJ$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>TMPCEDULA.C15</t>
   </si>
@@ -514,143 +514,12 @@
 SI-1
 NO-0</t>
   </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>230301</t>
-  </si>
-  <si>
-    <t>PORVENIR</t>
-  </si>
-  <si>
-    <t>N5</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>SALARIO LEY 100</t>
-  </si>
-  <si>
-    <t>230201</t>
-  </si>
-  <si>
-    <t>PROTECCION</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>BANCOLOMBIA</t>
-  </si>
-  <si>
-    <t>AGUILAR MARTHEY JOSE ORLANDO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MARTHEY</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>ORLANDO</t>
-  </si>
-  <si>
-    <t>CL 3 5 40</t>
-  </si>
-  <si>
-    <t>joseorlandoaguilarmarthey@gmail.com</t>
-  </si>
-  <si>
-    <t>54001</t>
-  </si>
-  <si>
-    <t>CUCUTA</t>
-  </si>
-  <si>
-    <t>007</t>
-  </si>
-  <si>
-    <t>ESCOLTA</t>
-  </si>
-  <si>
-    <t>1007</t>
-  </si>
-  <si>
-    <t>76978582601</t>
-  </si>
-  <si>
-    <t>0405</t>
-  </si>
-  <si>
-    <t>UNION TEMPORAL NCCTS 2026</t>
-  </si>
-  <si>
-    <t>EPS005</t>
-  </si>
-  <si>
-    <t>SANITAS</t>
-  </si>
-  <si>
-    <t>ARL AXA COLPATRIA</t>
-  </si>
-  <si>
-    <t>CCF37</t>
-  </si>
-  <si>
-    <t>COMFANORTE- CAJA DE COMPENSACI</t>
-  </si>
-  <si>
-    <t>88196928</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>OBRA LABOR</t>
-  </si>
-  <si>
-    <t>OCCIDENTE</t>
-  </si>
-  <si>
-    <t>L003</t>
-  </si>
-  <si>
-    <t>ESCOLTAS</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>CLIENTE EXTERNO</t>
-  </si>
-  <si>
-    <t>ACTIVIDADES DE SEGURIDAD PRIVADA, INCLUYE SERVICIOS DE GUARDIAS DE SEGURIDAD.</t>
-  </si>
-  <si>
-    <t>3108921091</t>
-  </si>
-  <si>
-    <t>14-04</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="11">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -673,14 +542,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -697,36 +558,8 @@
       <sz val="9"/>
       <name val="Times New Roman"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="8"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -736,12 +569,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -770,15 +597,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -816,71 +641,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
-    <cellStyle name="Moneda" xfId="5" builtinId="4"/>
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Normal 2 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Normal 3" xfId="4" xr:uid="{D51D5584-9622-4DB0-9554-03F0E241CF90}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Normal 2 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{D51D5584-9622-4DB0-9554-03F0E241CF90}"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -1199,7 +968,7 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:BJ3"/>
+  <dimension ref="A1:BJ2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1535,7 +1304,7 @@
       <c r="AA2" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="AB2" s="27" t="s">
+      <c r="AB2" s="13" t="s">
         <v>89</v>
       </c>
       <c r="AC2" s="8" t="s">
@@ -1639,186 +1408,6 @@
       </c>
       <c r="BJ2" s="8" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:62" s="15" customFormat="1" ht="12.6" customHeight="1">
-      <c r="A3" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="J3" s="16"/>
-      <c r="K3" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="N3" s="18">
-        <v>26393</v>
-      </c>
-      <c r="O3" s="19">
-        <v>46043</v>
-      </c>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="21">
-        <v>1</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="S3" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="U3" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="V3" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="W3" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="X3" s="22">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="AB3" s="28">
-        <v>3501810</v>
-      </c>
-      <c r="AC3" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="AD3" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE3" s="19">
-        <v>46043</v>
-      </c>
-      <c r="AF3" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG3" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="AH3" s="19">
-        <v>46043</v>
-      </c>
-      <c r="AI3" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="AJ3" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK3" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="AL3" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="AM3" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="AN3" s="16"/>
-      <c r="AO3" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="AP3" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ3" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="AR3" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="AS3" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="AT3" s="25">
-        <v>46171</v>
-      </c>
-      <c r="AU3" s="15">
-        <v>1</v>
-      </c>
-      <c r="AV3" s="15">
-        <v>1</v>
-      </c>
-      <c r="AW3" s="15">
-        <v>4</v>
-      </c>
-      <c r="AX3" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="AY3" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="AZ3" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="BA3" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="BB3" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="BC3" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="BD3" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="BE3" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="BF3" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="BG3" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="BH3" s="15">
-        <v>4801001</v>
-      </c>
-      <c r="BI3" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="BJ3" s="15">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1830,16 +1419,22 @@
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="K3" r:id="rId1" xr:uid="{CD9B215C-075B-48B2-B03E-AC7FD645FC7C}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D2281554FBC400488A53CD5E4CF21A4D" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="065bbd2080efe63d96717a72b278d73c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dbcdebb2-cf80-47cd-9ce4-da05099ac60d" xmlns:ns3="cb6b3d82-e657-49dc-ab00-8f11ccd10803" xmlns:ns4="01928591-29d3-40bf-897b-6c60acb0e16c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8c7732d0698db1a95db4353621cbd5f0" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="dbcdebb2-cf80-47cd-9ce4-da05099ac60d"/>
@@ -2099,15 +1694,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2120,6 +1706,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCF802FC-1CD7-42AF-A863-18B2CC423DDF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48D07738-D97B-46EB-A622-06D6123B5DFD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2139,14 +1733,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCF802FC-1CD7-42AF-A863-18B2CC423DDF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{949287C3-ECA2-45B9-9545-B08D69B2FC27}">
   <ds:schemaRefs>
